--- a/results/06_rf_corroboration/step5_random_forest_summary.xlsx
+++ b/results/06_rf_corroboration/step5_random_forest_summary.xlsx
@@ -90,22 +90,22 @@
     <t xml:space="preserve">Africa=105,Asia=215</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_predictions_queries.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_cv_summary.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_cv_perclass.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_cv_rows.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_variable_importance.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/FIG_RF_P1_macroregion_africa_vs_asia_validation_A4.pdf</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_predictions_queries.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_cv_summary.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_cv_perclass.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_cv_rows.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P1_macroregion_africa_vs_asia_variable_importance.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/FIG_RF_P1_macroregion_africa_vs_asia_validation_A4.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">P2_subregion_within_africa</t>
@@ -117,22 +117,22 @@
     <t xml:space="preserve">E_Africa=67,C_Africa=5,W_Africa=23,S_Africa=10</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_predictions_queries.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_cv_summary.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_cv_perclass.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_cv_rows.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_variable_importance.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/FIG_RF_P2_subregion_within_africa_validation_A4.pdf</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_predictions_queries.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_cv_summary.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_cv_perclass.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_cv_rows.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P2_subregion_within_africa_variable_importance.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/FIG_RF_P2_subregion_within_africa_validation_A4.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">P3_subregion_within_asia</t>
@@ -141,22 +141,22 @@
     <t xml:space="preserve">SE_Asia=90,S_Asia=45,E_Asia=80</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_predictions_queries.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_cv_summary.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_cv_perclass.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_cv_rows.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_variable_importance.tsv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration/FIG_RF_P3_subregion_within_asia_validation_A4.pdf</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_predictions_queries.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_cv_summary.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_cv_perclass.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_cv_rows.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/RF_P3_subregion_within_asia_variable_importance.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration/FIG_RF_P3_subregion_within_asia_validation_A4.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">sample_id</t>
@@ -240,78 +240,78 @@
     <t xml:space="preserve">Asia</t>
   </si>
   <si>
+    <t xml:space="preserve">Moderate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E_Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncertain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low_global_K_agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2_Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supports_step4_macroregion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bd_2023_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S_Asia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3_Asia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bd_2023_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E_Asia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bd_2023_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bd_2023_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">too_few_usable_K</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">macroregion_uncertain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">step4_macroregion_uncertain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bd_2023_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Low</t>
   </si>
   <si>
-    <t xml:space="preserve">ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belgium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E_Africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncertain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">low_global_K_agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2_Africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">supports_step4_macroregion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bd_2023_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S_Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3_Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bd_2023_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E_Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bd_2023_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bd_2023_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">too_few_usable_K</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">macroregion_uncertain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">step4_macroregion_uncertain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bd_2023_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bd_2023_3</t>
   </si>
   <si>
@@ -417,25 +417,25 @@
     <t xml:space="preserve">qc_dir</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/01_qc</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/01_qc</t>
   </si>
   <si>
     <t xml:space="preserve">step3_dir</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/02_snp_panels</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/02_snp_panels</t>
   </si>
   <si>
     <t xml:space="preserve">step4_dir</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/04_origin_assignment</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/04_origin_assignment</t>
   </si>
   <si>
     <t xml:space="preserve">out_dir</t>
   </si>
   <si>
-    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/PESTFLY_origin_tracing_MolEcolRes_publication_pipeline/results/06_rf_corroboration</t>
+    <t xml:space="preserve">C:/Users/virgilio/Documents/GitHub/PESTFLY/000_REVISION_JPS_PESTFLY_origin_tracing_pipeline/results/06_rf_corroboration</t>
   </si>
   <si>
     <t xml:space="preserve">panels</t>
@@ -1063,19 +1063,19 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.942100625</v>
+        <v>0.942136875</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -1125,7 +1125,7 @@
         <v>0.72952380952381</v>
       </c>
       <c r="J3" t="n">
-        <v>0.617687619047619</v>
+        <v>0.617142857142857</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O3" t="s">
         <v>33</v>
@@ -1184,10 +1184,10 @@
         <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>0.96093023255814</v>
+        <v>0.965581395348837</v>
       </c>
       <c r="J4" t="n">
-        <v>0.67437023255814</v>
+        <v>0.672928372093023</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1328,16 +1328,16 @@
         <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>0.846</v>
+        <v>0.866</v>
       </c>
       <c r="D2" t="s">
         <v>73</v>
       </c>
       <c r="E2" t="n">
-        <v>0.154</v>
+        <v>0.134</v>
       </c>
       <c r="F2" t="n">
-        <v>0.692</v>
+        <v>0.732</v>
       </c>
       <c r="G2" t="n">
         <v>11081</v>
@@ -1500,16 +1500,16 @@
         <v>73</v>
       </c>
       <c r="C4" t="n">
-        <v>0.967</v>
+        <v>0.953</v>
       </c>
       <c r="D4" t="s">
         <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>0.033</v>
+        <v>0.047</v>
       </c>
       <c r="F4" t="n">
-        <v>0.934</v>
+        <v>0.906</v>
       </c>
       <c r="G4" t="n">
         <v>11080</v>
@@ -1672,22 +1672,22 @@
         <v>73</v>
       </c>
       <c r="C6" t="n">
-        <v>0.891</v>
+        <v>0.899</v>
       </c>
       <c r="D6" t="s">
         <v>72</v>
       </c>
       <c r="E6" t="n">
-        <v>0.109</v>
+        <v>0.101</v>
       </c>
       <c r="F6" t="n">
-        <v>0.782</v>
+        <v>0.798</v>
       </c>
       <c r="G6" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
         <v>20</v>
@@ -1720,56 +1720,56 @@
         <v>81</v>
       </c>
       <c r="S6" t="s">
+        <v>92</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="s">
         <v>93</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="s">
-        <v>94</v>
       </c>
       <c r="W6" t="s">
         <v>81</v>
       </c>
       <c r="X6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z6"/>
       <c r="AA6"/>
       <c r="AB6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>0.594</v>
+        <v>0.606</v>
       </c>
       <c r="D7" t="s">
         <v>72</v>
       </c>
       <c r="E7" t="n">
-        <v>0.406</v>
+        <v>0.394</v>
       </c>
       <c r="F7" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
       <c r="G7" t="n">
         <v>3292</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I7" t="s">
         <v>20</v>
@@ -1802,30 +1802,30 @@
         <v>81</v>
       </c>
       <c r="S7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="s">
         <v>93</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="s">
-        <v>94</v>
       </c>
       <c r="W7" t="s">
         <v>81</v>
       </c>
       <c r="X7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z7"/>
       <c r="AA7"/>
       <c r="AB7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -1836,22 +1836,22 @@
         <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>0.898</v>
+        <v>0.897</v>
       </c>
       <c r="D8" t="s">
         <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="F8" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="G8" t="n">
-        <v>2883</v>
+        <v>2879</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
@@ -1884,30 +1884,30 @@
         <v>81</v>
       </c>
       <c r="S8" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="s">
         <v>93</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="s">
-        <v>94</v>
       </c>
       <c r="W8" t="s">
         <v>81</v>
       </c>
       <c r="X8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z8"/>
       <c r="AA8"/>
       <c r="AB8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -1918,16 +1918,16 @@
         <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>0.97</v>
+        <v>0.965</v>
       </c>
       <c r="D9" t="s">
         <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="F9" t="n">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="G9" t="n">
         <v>11069</v>
@@ -2004,22 +2004,22 @@
         <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>0.862</v>
+        <v>0.886</v>
       </c>
       <c r="D10" t="s">
         <v>73</v>
       </c>
       <c r="E10" t="n">
-        <v>0.138</v>
+        <v>0.114</v>
       </c>
       <c r="F10" t="n">
-        <v>0.724</v>
+        <v>0.772</v>
       </c>
       <c r="G10" t="n">
-        <v>11064</v>
+        <v>11063</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
         <v>20</v>
@@ -2073,10 +2073,10 @@
         <v>83</v>
       </c>
       <c r="Z10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA10" t="n">
         <v>0.666666666666667</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1</v>
       </c>
       <c r="AB10" t="s">
         <v>84</v>
@@ -2090,22 +2090,22 @@
         <v>73</v>
       </c>
       <c r="C11" t="n">
-        <v>0.882</v>
+        <v>0.868</v>
       </c>
       <c r="D11" t="s">
         <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>0.118</v>
+        <v>0.132</v>
       </c>
       <c r="F11" t="n">
-        <v>0.764</v>
+        <v>0.736</v>
       </c>
       <c r="G11" t="n">
         <v>11075</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
         <v>20</v>
@@ -2176,22 +2176,22 @@
         <v>73</v>
       </c>
       <c r="C12" t="n">
-        <v>0.914</v>
+        <v>0.925</v>
       </c>
       <c r="D12" t="s">
         <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>0.086</v>
+        <v>0.075</v>
       </c>
       <c r="F12" t="n">
-        <v>0.828</v>
+        <v>0.85</v>
       </c>
       <c r="G12" t="n">
         <v>11079</v>
       </c>
       <c r="H12" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
@@ -2262,22 +2262,22 @@
         <v>72</v>
       </c>
       <c r="C13" t="n">
-        <v>0.881</v>
+        <v>0.865</v>
       </c>
       <c r="D13" t="s">
         <v>73</v>
       </c>
       <c r="E13" t="n">
-        <v>0.119</v>
+        <v>0.135</v>
       </c>
       <c r="F13" t="n">
-        <v>0.762</v>
+        <v>0.73</v>
       </c>
       <c r="G13" t="n">
         <v>11073</v>
       </c>
       <c r="H13" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I13" t="s">
         <v>20</v>
@@ -2348,22 +2348,22 @@
         <v>72</v>
       </c>
       <c r="C14" t="n">
-        <v>0.894</v>
+        <v>0.889</v>
       </c>
       <c r="D14" t="s">
         <v>73</v>
       </c>
       <c r="E14" t="n">
-        <v>0.106</v>
+        <v>0.111</v>
       </c>
       <c r="F14" t="n">
-        <v>0.788</v>
+        <v>0.778</v>
       </c>
       <c r="G14" t="n">
         <v>11069</v>
       </c>
       <c r="H14" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
         <v>20</v>
@@ -2417,7 +2417,7 @@
         <v>83</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.5</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="AA14" t="n">
         <v>1</v>
@@ -2434,22 +2434,22 @@
         <v>72</v>
       </c>
       <c r="C15" t="n">
-        <v>0.858</v>
+        <v>0.861</v>
       </c>
       <c r="D15" t="s">
         <v>73</v>
       </c>
       <c r="E15" t="n">
-        <v>0.142</v>
+        <v>0.139</v>
       </c>
       <c r="F15" t="n">
-        <v>0.716</v>
+        <v>0.722</v>
       </c>
       <c r="G15" t="n">
         <v>11078</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
@@ -2520,19 +2520,19 @@
         <v>72</v>
       </c>
       <c r="C16" t="n">
-        <v>0.844</v>
+        <v>0.861</v>
       </c>
       <c r="D16" t="s">
         <v>73</v>
       </c>
       <c r="E16" t="n">
-        <v>0.156</v>
+        <v>0.139</v>
       </c>
       <c r="F16" t="n">
-        <v>0.688</v>
+        <v>0.722</v>
       </c>
       <c r="G16" t="n">
-        <v>11070</v>
+        <v>11071</v>
       </c>
       <c r="H16" t="s">
         <v>74</v>
@@ -2606,16 +2606,16 @@
         <v>72</v>
       </c>
       <c r="C17" t="n">
-        <v>0.838</v>
+        <v>0.854</v>
       </c>
       <c r="D17" t="s">
         <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>0.162</v>
+        <v>0.146</v>
       </c>
       <c r="F17" t="n">
-        <v>0.676</v>
+        <v>0.708</v>
       </c>
       <c r="G17" t="n">
         <v>11071</v>
@@ -2707,7 +2707,7 @@
         <v>11074</v>
       </c>
       <c r="H18" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I18" t="s">
         <v>20</v>
@@ -2778,22 +2778,22 @@
         <v>72</v>
       </c>
       <c r="C19" t="n">
-        <v>0.874</v>
+        <v>0.846</v>
       </c>
       <c r="D19" t="s">
         <v>73</v>
       </c>
       <c r="E19" t="n">
-        <v>0.126</v>
+        <v>0.154</v>
       </c>
       <c r="F19" t="n">
-        <v>0.748</v>
+        <v>0.692</v>
       </c>
       <c r="G19" t="n">
         <v>11075</v>
       </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I19" t="s">
         <v>20</v>
@@ -2864,22 +2864,22 @@
         <v>72</v>
       </c>
       <c r="C20" t="n">
-        <v>0.863</v>
+        <v>0.874</v>
       </c>
       <c r="D20" t="s">
         <v>73</v>
       </c>
       <c r="E20" t="n">
-        <v>0.137</v>
+        <v>0.126</v>
       </c>
       <c r="F20" t="n">
-        <v>0.726</v>
+        <v>0.748</v>
       </c>
       <c r="G20" t="n">
         <v>11076</v>
       </c>
       <c r="H20" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I20" t="s">
         <v>20</v>
@@ -2950,22 +2950,22 @@
         <v>72</v>
       </c>
       <c r="C21" t="n">
-        <v>0.83</v>
+        <v>0.835</v>
       </c>
       <c r="D21" t="s">
         <v>73</v>
       </c>
       <c r="E21" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="F21" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="G21" t="n">
         <v>11070</v>
       </c>
       <c r="H21" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I21" t="s">
         <v>20</v>
@@ -3036,22 +3036,22 @@
         <v>72</v>
       </c>
       <c r="C22" t="n">
-        <v>0.873</v>
+        <v>0.885</v>
       </c>
       <c r="D22" t="s">
         <v>73</v>
       </c>
       <c r="E22" t="n">
-        <v>0.127</v>
+        <v>0.115</v>
       </c>
       <c r="F22" t="n">
-        <v>0.746</v>
+        <v>0.77</v>
       </c>
       <c r="G22" t="n">
-        <v>11063</v>
+        <v>11062</v>
       </c>
       <c r="H22" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
@@ -3122,22 +3122,22 @@
         <v>73</v>
       </c>
       <c r="C23" t="n">
-        <v>0.942</v>
+        <v>0.933</v>
       </c>
       <c r="D23" t="s">
         <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>0.058</v>
+        <v>0.067</v>
       </c>
       <c r="F23" t="n">
-        <v>0.884</v>
+        <v>0.866</v>
       </c>
       <c r="G23" t="n">
         <v>11066</v>
       </c>
       <c r="H23" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s">
         <v>20</v>
@@ -3208,22 +3208,22 @@
         <v>80</v>
       </c>
       <c r="C24" t="n">
-        <v>0.531</v>
+        <v>0.528</v>
       </c>
       <c r="D24" t="s">
         <v>104</v>
       </c>
       <c r="E24" t="n">
-        <v>0.321</v>
+        <v>0.323</v>
       </c>
       <c r="F24" t="n">
-        <v>0.21</v>
+        <v>0.205</v>
       </c>
       <c r="G24" t="n">
         <v>10992</v>
       </c>
       <c r="H24" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I24" t="s">
         <v>30</v>
@@ -3294,16 +3294,16 @@
         <v>80</v>
       </c>
       <c r="C25" t="n">
-        <v>0.519</v>
+        <v>0.523</v>
       </c>
       <c r="D25" t="s">
         <v>104</v>
       </c>
       <c r="E25" t="n">
-        <v>0.346</v>
+        <v>0.333</v>
       </c>
       <c r="F25" t="n">
-        <v>0.173</v>
+        <v>0.19</v>
       </c>
       <c r="G25" t="n">
         <v>10968</v>
@@ -3380,22 +3380,22 @@
         <v>80</v>
       </c>
       <c r="C26" t="n">
-        <v>0.554</v>
+        <v>0.542</v>
       </c>
       <c r="D26" t="s">
         <v>104</v>
       </c>
       <c r="E26" t="n">
-        <v>0.302</v>
+        <v>0.309</v>
       </c>
       <c r="F26" t="n">
-        <v>0.252</v>
+        <v>0.233</v>
       </c>
       <c r="G26" t="n">
-        <v>10960</v>
+        <v>10958</v>
       </c>
       <c r="H26" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I26" t="s">
         <v>30</v>
@@ -3466,13 +3466,13 @@
         <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>0.551</v>
+        <v>0.535</v>
       </c>
       <c r="D27" t="s">
         <v>104</v>
       </c>
       <c r="E27" t="n">
-        <v>0.303</v>
+        <v>0.287</v>
       </c>
       <c r="F27" t="n">
         <v>0.248</v>
@@ -3481,7 +3481,7 @@
         <v>10965</v>
       </c>
       <c r="H27" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I27" t="s">
         <v>30</v>
@@ -3552,22 +3552,22 @@
         <v>80</v>
       </c>
       <c r="C28" t="n">
-        <v>0.594</v>
+        <v>0.582</v>
       </c>
       <c r="D28" t="s">
         <v>104</v>
       </c>
       <c r="E28" t="n">
-        <v>0.349</v>
+        <v>0.354</v>
       </c>
       <c r="F28" t="n">
-        <v>0.245</v>
+        <v>0.228</v>
       </c>
       <c r="G28" t="n">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="H28" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I28" t="s">
         <v>30</v>
@@ -3600,25 +3600,25 @@
         <v>81</v>
       </c>
       <c r="S28" t="s">
+        <v>92</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="s">
         <v>93</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="s">
-        <v>94</v>
       </c>
       <c r="W28" t="s">
         <v>81</v>
       </c>
       <c r="X28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z28"/>
       <c r="AA28"/>
@@ -3628,28 +3628,28 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
         <v>80</v>
       </c>
       <c r="C29" t="n">
-        <v>0.585</v>
+        <v>0.58</v>
       </c>
       <c r="D29" t="s">
         <v>104</v>
       </c>
       <c r="E29" t="n">
-        <v>0.337</v>
+        <v>0.33</v>
       </c>
       <c r="F29" t="n">
-        <v>0.248</v>
+        <v>0.25</v>
       </c>
       <c r="G29" t="n">
-        <v>3282</v>
+        <v>3313</v>
       </c>
       <c r="H29" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I29" t="s">
         <v>30</v>
@@ -3682,25 +3682,25 @@
         <v>81</v>
       </c>
       <c r="S29" t="s">
+        <v>92</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="s">
         <v>93</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="s">
-        <v>94</v>
       </c>
       <c r="W29" t="s">
         <v>81</v>
       </c>
       <c r="X29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z29"/>
       <c r="AA29"/>
@@ -3716,22 +3716,22 @@
         <v>80</v>
       </c>
       <c r="C30" t="n">
-        <v>0.576</v>
+        <v>0.573</v>
       </c>
       <c r="D30" t="s">
         <v>104</v>
       </c>
       <c r="E30" t="n">
-        <v>0.338</v>
+        <v>0.347</v>
       </c>
       <c r="F30" t="n">
-        <v>0.238</v>
+        <v>0.226</v>
       </c>
       <c r="G30" t="n">
-        <v>2872</v>
+        <v>2884</v>
       </c>
       <c r="H30" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I30" t="s">
         <v>30</v>
@@ -3764,25 +3764,25 @@
         <v>81</v>
       </c>
       <c r="S30" t="s">
+        <v>92</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="s">
         <v>93</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" t="s">
-        <v>94</v>
       </c>
       <c r="W30" t="s">
         <v>81</v>
       </c>
       <c r="X30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z30"/>
       <c r="AA30"/>
@@ -3798,22 +3798,22 @@
         <v>80</v>
       </c>
       <c r="C31" t="n">
-        <v>0.531</v>
+        <v>0.492</v>
       </c>
       <c r="D31" t="s">
         <v>104</v>
       </c>
       <c r="E31" t="n">
-        <v>0.301</v>
+        <v>0.356</v>
       </c>
       <c r="F31" t="n">
-        <v>0.23</v>
+        <v>0.136</v>
       </c>
       <c r="G31" t="n">
         <v>10956</v>
       </c>
       <c r="H31" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s">
         <v>30</v>
@@ -3884,22 +3884,22 @@
         <v>80</v>
       </c>
       <c r="C32" t="n">
-        <v>0.579</v>
+        <v>0.555</v>
       </c>
       <c r="D32" t="s">
         <v>104</v>
       </c>
       <c r="E32" t="n">
-        <v>0.29</v>
+        <v>0.308</v>
       </c>
       <c r="F32" t="n">
-        <v>0.289</v>
+        <v>0.247</v>
       </c>
       <c r="G32" t="n">
         <v>10984</v>
       </c>
       <c r="H32" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I32" t="s">
         <v>30</v>
@@ -3953,10 +3953,10 @@
         <v>83</v>
       </c>
       <c r="Z32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA32" t="n">
         <v>0.666666666666667</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1</v>
       </c>
       <c r="AB32" t="s">
         <v>115</v>
@@ -3970,22 +3970,22 @@
         <v>80</v>
       </c>
       <c r="C33" t="n">
-        <v>0.578</v>
+        <v>0.576</v>
       </c>
       <c r="D33" t="s">
         <v>104</v>
       </c>
       <c r="E33" t="n">
-        <v>0.276</v>
+        <v>0.293</v>
       </c>
       <c r="F33" t="n">
-        <v>0.302</v>
+        <v>0.283</v>
       </c>
       <c r="G33" t="n">
-        <v>10957</v>
+        <v>10958</v>
       </c>
       <c r="H33" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I33" t="s">
         <v>30</v>
@@ -4056,22 +4056,22 @@
         <v>80</v>
       </c>
       <c r="C34" t="n">
-        <v>0.567</v>
+        <v>0.514</v>
       </c>
       <c r="D34" t="s">
         <v>104</v>
       </c>
       <c r="E34" t="n">
-        <v>0.322</v>
+        <v>0.362</v>
       </c>
       <c r="F34" t="n">
-        <v>0.245</v>
+        <v>0.152</v>
       </c>
       <c r="G34" t="n">
         <v>10963</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I34" t="s">
         <v>30</v>
@@ -4142,22 +4142,22 @@
         <v>80</v>
       </c>
       <c r="C35" t="n">
-        <v>0.522</v>
+        <v>0.497</v>
       </c>
       <c r="D35" t="s">
         <v>104</v>
       </c>
       <c r="E35" t="n">
-        <v>0.311</v>
+        <v>0.308</v>
       </c>
       <c r="F35" t="n">
-        <v>0.211</v>
+        <v>0.189</v>
       </c>
       <c r="G35" t="n">
-        <v>10992</v>
+        <v>10991</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s">
         <v>30</v>
@@ -4228,22 +4228,22 @@
         <v>80</v>
       </c>
       <c r="C36" t="n">
-        <v>0.546</v>
+        <v>0.555</v>
       </c>
       <c r="D36" t="s">
         <v>104</v>
       </c>
       <c r="E36" t="n">
-        <v>0.311</v>
+        <v>0.292</v>
       </c>
       <c r="F36" t="n">
-        <v>0.235</v>
+        <v>0.263</v>
       </c>
       <c r="G36" t="n">
         <v>10991</v>
       </c>
       <c r="H36" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I36" t="s">
         <v>30</v>
@@ -4297,7 +4297,7 @@
         <v>83</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.5</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="AA36" t="n">
         <v>1</v>
@@ -4314,16 +4314,16 @@
         <v>80</v>
       </c>
       <c r="C37" t="n">
-        <v>0.484</v>
+        <v>0.517</v>
       </c>
       <c r="D37" t="s">
         <v>104</v>
       </c>
       <c r="E37" t="n">
-        <v>0.349</v>
+        <v>0.324</v>
       </c>
       <c r="F37" t="n">
-        <v>0.135</v>
+        <v>0.193</v>
       </c>
       <c r="G37" t="n">
         <v>10992</v>
@@ -4400,16 +4400,16 @@
         <v>80</v>
       </c>
       <c r="C38" t="n">
-        <v>0.443</v>
+        <v>0.446</v>
       </c>
       <c r="D38" t="s">
         <v>104</v>
       </c>
       <c r="E38" t="n">
-        <v>0.361</v>
+        <v>0.338</v>
       </c>
       <c r="F38" t="n">
-        <v>0.082</v>
+        <v>0.108</v>
       </c>
       <c r="G38" t="n">
         <v>10991</v>
@@ -4486,22 +4486,22 @@
         <v>80</v>
       </c>
       <c r="C39" t="n">
-        <v>0.573</v>
+        <v>0.567</v>
       </c>
       <c r="D39" t="s">
         <v>104</v>
       </c>
       <c r="E39" t="n">
-        <v>0.271</v>
+        <v>0.234</v>
       </c>
       <c r="F39" t="n">
-        <v>0.302</v>
+        <v>0.333</v>
       </c>
       <c r="G39" t="n">
-        <v>10984</v>
+        <v>10983</v>
       </c>
       <c r="H39" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I39" t="s">
         <v>30</v>
@@ -4572,16 +4572,16 @@
         <v>80</v>
       </c>
       <c r="C40" t="n">
-        <v>0.464</v>
+        <v>0.444</v>
       </c>
       <c r="D40" t="s">
         <v>104</v>
       </c>
       <c r="E40" t="n">
-        <v>0.37</v>
+        <v>0.338</v>
       </c>
       <c r="F40" t="n">
-        <v>0.094</v>
+        <v>0.106</v>
       </c>
       <c r="G40" t="n">
         <v>10984</v>
@@ -4658,22 +4658,22 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>0.571</v>
+        <v>0.573</v>
       </c>
       <c r="D41" t="s">
         <v>104</v>
       </c>
       <c r="E41" t="n">
-        <v>0.239</v>
+        <v>0.23</v>
       </c>
       <c r="F41" t="n">
-        <v>0.332</v>
+        <v>0.343</v>
       </c>
       <c r="G41" t="n">
         <v>10993</v>
       </c>
       <c r="H41" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I41" t="s">
         <v>30</v>
@@ -4744,16 +4744,16 @@
         <v>80</v>
       </c>
       <c r="C42" t="n">
-        <v>0.485</v>
+        <v>0.47</v>
       </c>
       <c r="D42" t="s">
         <v>104</v>
       </c>
       <c r="E42" t="n">
-        <v>0.317</v>
+        <v>0.344</v>
       </c>
       <c r="F42" t="n">
-        <v>0.168</v>
+        <v>0.126</v>
       </c>
       <c r="G42" t="n">
         <v>10997</v>
@@ -4830,19 +4830,19 @@
         <v>80</v>
       </c>
       <c r="C43" t="n">
-        <v>0.498</v>
+        <v>0.497</v>
       </c>
       <c r="D43" t="s">
         <v>104</v>
       </c>
       <c r="E43" t="n">
-        <v>0.33</v>
+        <v>0.343</v>
       </c>
       <c r="F43" t="n">
-        <v>0.168</v>
+        <v>0.154</v>
       </c>
       <c r="G43" t="n">
-        <v>10981</v>
+        <v>10980</v>
       </c>
       <c r="H43" t="s">
         <v>81</v>
@@ -4916,19 +4916,19 @@
         <v>80</v>
       </c>
       <c r="C44" t="n">
-        <v>0.496</v>
+        <v>0.441</v>
       </c>
       <c r="D44" t="s">
         <v>104</v>
       </c>
       <c r="E44" t="n">
-        <v>0.368</v>
+        <v>0.414</v>
       </c>
       <c r="F44" t="n">
-        <v>0.128</v>
+        <v>0.027</v>
       </c>
       <c r="G44" t="n">
-        <v>10973</v>
+        <v>10974</v>
       </c>
       <c r="H44" t="s">
         <v>81</v>
@@ -5002,19 +5002,19 @@
         <v>80</v>
       </c>
       <c r="C45" t="n">
-        <v>0.507</v>
+        <v>0.487</v>
       </c>
       <c r="D45" t="s">
         <v>104</v>
       </c>
       <c r="E45" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="F45" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="G45" t="n">
-        <v>10955</v>
+        <v>10957</v>
       </c>
       <c r="H45" t="s">
         <v>81</v>
@@ -5088,22 +5088,22 @@
         <v>119</v>
       </c>
       <c r="C46" t="n">
-        <v>0.48</v>
+        <v>0.503</v>
       </c>
       <c r="D46" t="s">
         <v>86</v>
       </c>
       <c r="E46" t="n">
-        <v>0.282</v>
+        <v>0.265</v>
       </c>
       <c r="F46" t="n">
-        <v>0.198</v>
+        <v>0.238</v>
       </c>
       <c r="G46" t="n">
-        <v>11072</v>
+        <v>11071</v>
       </c>
       <c r="H46" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I46" t="s">
         <v>39</v>
@@ -5174,19 +5174,19 @@
         <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>0.41</v>
+        <v>0.417</v>
       </c>
       <c r="D47" t="s">
         <v>119</v>
       </c>
       <c r="E47" t="n">
-        <v>0.325</v>
+        <v>0.311</v>
       </c>
       <c r="F47" t="n">
-        <v>0.085</v>
+        <v>0.106</v>
       </c>
       <c r="G47" t="n">
-        <v>11069</v>
+        <v>11070</v>
       </c>
       <c r="H47" t="s">
         <v>81</v>
@@ -5260,19 +5260,19 @@
         <v>89</v>
       </c>
       <c r="C48" t="n">
-        <v>0.409</v>
+        <v>0.398</v>
       </c>
       <c r="D48" t="s">
         <v>119</v>
       </c>
       <c r="E48" t="n">
-        <v>0.374</v>
+        <v>0.365</v>
       </c>
       <c r="F48" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="G48" t="n">
-        <v>11071</v>
+        <v>11070</v>
       </c>
       <c r="H48" t="s">
         <v>81</v>
@@ -5346,22 +5346,22 @@
         <v>86</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="D49" t="s">
         <v>119</v>
       </c>
       <c r="E49" t="n">
-        <v>0.299</v>
+        <v>0.311</v>
       </c>
       <c r="F49" t="n">
-        <v>0.201</v>
+        <v>0.167</v>
       </c>
       <c r="G49" t="n">
-        <v>11074</v>
+        <v>11075</v>
       </c>
       <c r="H49" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I49" t="s">
         <v>39</v>
@@ -5438,16 +5438,16 @@
         <v>89</v>
       </c>
       <c r="E50" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="F50" t="n">
-        <v>0.71</v>
+        <v>0.708</v>
       </c>
       <c r="G50" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H50" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I50" t="s">
         <v>39</v>
@@ -5480,25 +5480,25 @@
         <v>81</v>
       </c>
       <c r="S50" t="s">
+        <v>92</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
         <v>93</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" t="s">
-        <v>94</v>
       </c>
       <c r="W50" t="s">
         <v>81</v>
       </c>
       <c r="X50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z50"/>
       <c r="AA50"/>
@@ -5508,28 +5508,28 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" t="s">
         <v>119</v>
       </c>
       <c r="C51" t="n">
-        <v>0.699</v>
+        <v>0.695</v>
       </c>
       <c r="D51" t="s">
         <v>89</v>
       </c>
       <c r="E51" t="n">
-        <v>0.184</v>
+        <v>0.181</v>
       </c>
       <c r="F51" t="n">
-        <v>0.515</v>
+        <v>0.514</v>
       </c>
       <c r="G51" t="n">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="H51" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I51" t="s">
         <v>39</v>
@@ -5562,25 +5562,25 @@
         <v>81</v>
       </c>
       <c r="S51" t="s">
+        <v>92</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="s">
         <v>93</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="s">
-        <v>94</v>
       </c>
       <c r="W51" t="s">
         <v>81</v>
       </c>
       <c r="X51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z51"/>
       <c r="AA51"/>
@@ -5596,22 +5596,22 @@
         <v>119</v>
       </c>
       <c r="C52" t="n">
-        <v>0.643</v>
+        <v>0.623</v>
       </c>
       <c r="D52" t="s">
         <v>89</v>
       </c>
       <c r="E52" t="n">
-        <v>0.241</v>
+        <v>0.251</v>
       </c>
       <c r="F52" t="n">
-        <v>0.402</v>
+        <v>0.372</v>
       </c>
       <c r="G52" t="n">
-        <v>2903</v>
+        <v>2892</v>
       </c>
       <c r="H52" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I52" t="s">
         <v>39</v>
@@ -5644,25 +5644,25 @@
         <v>81</v>
       </c>
       <c r="S52" t="s">
+        <v>92</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
         <v>93</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" t="s">
-        <v>94</v>
       </c>
       <c r="W52" t="s">
         <v>81</v>
       </c>
       <c r="X52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Y52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z52"/>
       <c r="AA52"/>
@@ -5678,19 +5678,19 @@
         <v>86</v>
       </c>
       <c r="C53" t="n">
-        <v>0.355</v>
+        <v>0.39</v>
       </c>
       <c r="D53" t="s">
         <v>119</v>
       </c>
       <c r="E53" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="F53" t="n">
-        <v>0.011</v>
+        <v>0.048</v>
       </c>
       <c r="G53" t="n">
-        <v>11060</v>
+        <v>11059</v>
       </c>
       <c r="H53" t="s">
         <v>81</v>
@@ -5764,19 +5764,19 @@
         <v>119</v>
       </c>
       <c r="C54" t="n">
-        <v>0.427</v>
+        <v>0.459</v>
       </c>
       <c r="D54" t="s">
         <v>86</v>
       </c>
       <c r="E54" t="n">
-        <v>0.344</v>
+        <v>0.325</v>
       </c>
       <c r="F54" t="n">
-        <v>0.083</v>
+        <v>0.134</v>
       </c>
       <c r="G54" t="n">
-        <v>11058</v>
+        <v>11057</v>
       </c>
       <c r="H54" t="s">
         <v>81</v>
@@ -5833,10 +5833,10 @@
         <v>83</v>
       </c>
       <c r="Z54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA54" t="n">
         <v>0.666666666666667</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1</v>
       </c>
       <c r="AB54" t="s">
         <v>120</v>
@@ -5850,7 +5850,7 @@
         <v>119</v>
       </c>
       <c r="C55" t="n">
-        <v>0.418</v>
+        <v>0.401</v>
       </c>
       <c r="D55" t="s">
         <v>86</v>
@@ -5859,10 +5859,10 @@
         <v>0.36</v>
       </c>
       <c r="F55" t="n">
-        <v>0.058</v>
+        <v>0.041</v>
       </c>
       <c r="G55" t="n">
-        <v>11073</v>
+        <v>11074</v>
       </c>
       <c r="H55" t="s">
         <v>81</v>
@@ -5936,19 +5936,19 @@
         <v>89</v>
       </c>
       <c r="C56" t="n">
-        <v>0.391</v>
+        <v>0.364</v>
       </c>
       <c r="D56" t="s">
         <v>86</v>
       </c>
       <c r="E56" t="n">
-        <v>0.307</v>
+        <v>0.326</v>
       </c>
       <c r="F56" t="n">
-        <v>0.084</v>
+        <v>0.038</v>
       </c>
       <c r="G56" t="n">
-        <v>11076</v>
+        <v>11077</v>
       </c>
       <c r="H56" t="s">
         <v>81</v>
@@ -6022,16 +6022,16 @@
         <v>86</v>
       </c>
       <c r="C57" t="n">
-        <v>0.48</v>
+        <v>0.488</v>
       </c>
       <c r="D57" t="s">
         <v>119</v>
       </c>
       <c r="E57" t="n">
-        <v>0.341</v>
+        <v>0.317</v>
       </c>
       <c r="F57" t="n">
-        <v>0.139</v>
+        <v>0.171</v>
       </c>
       <c r="G57" t="n">
         <v>11072</v>
@@ -6108,19 +6108,19 @@
         <v>119</v>
       </c>
       <c r="C58" t="n">
-        <v>0.446</v>
+        <v>0.428</v>
       </c>
       <c r="D58" t="s">
         <v>86</v>
       </c>
       <c r="E58" t="n">
-        <v>0.391</v>
+        <v>0.39</v>
       </c>
       <c r="F58" t="n">
-        <v>0.055</v>
+        <v>0.038</v>
       </c>
       <c r="G58" t="n">
-        <v>11073</v>
+        <v>11075</v>
       </c>
       <c r="H58" t="s">
         <v>81</v>
@@ -6177,7 +6177,7 @@
         <v>83</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.5</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="AA58" t="n">
         <v>1</v>
@@ -6194,16 +6194,16 @@
         <v>119</v>
       </c>
       <c r="C59" t="n">
-        <v>0.437</v>
+        <v>0.449</v>
       </c>
       <c r="D59" t="s">
         <v>86</v>
       </c>
       <c r="E59" t="n">
-        <v>0.319</v>
+        <v>0.334</v>
       </c>
       <c r="F59" t="n">
-        <v>0.118</v>
+        <v>0.115</v>
       </c>
       <c r="G59" t="n">
         <v>11070</v>
@@ -6277,22 +6277,22 @@
         <v>107</v>
       </c>
       <c r="B60" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="D60" t="s">
         <v>86</v>
       </c>
-      <c r="C60" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D60" t="s">
-        <v>119</v>
-      </c>
       <c r="E60" t="n">
-        <v>0.395</v>
+        <v>0.385</v>
       </c>
       <c r="F60" t="n">
-        <v>0.005</v>
+        <v>0.019</v>
       </c>
       <c r="G60" t="n">
-        <v>11071</v>
+        <v>11070</v>
       </c>
       <c r="H60" t="s">
         <v>81</v>
@@ -6366,19 +6366,19 @@
         <v>119</v>
       </c>
       <c r="C61" t="n">
-        <v>0.425</v>
+        <v>0.418</v>
       </c>
       <c r="D61" t="s">
         <v>86</v>
       </c>
       <c r="E61" t="n">
-        <v>0.357</v>
+        <v>0.369</v>
       </c>
       <c r="F61" t="n">
-        <v>0.068</v>
+        <v>0.049</v>
       </c>
       <c r="G61" t="n">
-        <v>11058</v>
+        <v>11060</v>
       </c>
       <c r="H61" t="s">
         <v>81</v>
@@ -6452,19 +6452,19 @@
         <v>86</v>
       </c>
       <c r="C62" t="n">
-        <v>0.418</v>
+        <v>0.442</v>
       </c>
       <c r="D62" t="s">
         <v>119</v>
       </c>
       <c r="E62" t="n">
-        <v>0.366</v>
+        <v>0.339</v>
       </c>
       <c r="F62" t="n">
-        <v>0.052</v>
+        <v>0.103</v>
       </c>
       <c r="G62" t="n">
-        <v>11065</v>
+        <v>11064</v>
       </c>
       <c r="H62" t="s">
         <v>81</v>
@@ -6538,19 +6538,19 @@
         <v>119</v>
       </c>
       <c r="C63" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="D63" t="s">
         <v>86</v>
       </c>
       <c r="E63" t="n">
-        <v>0.344</v>
+        <v>0.322</v>
       </c>
       <c r="F63" t="n">
-        <v>0.084</v>
+        <v>0.105</v>
       </c>
       <c r="G63" t="n">
-        <v>11069</v>
+        <v>11067</v>
       </c>
       <c r="H63" t="s">
         <v>81</v>
@@ -6624,19 +6624,19 @@
         <v>119</v>
       </c>
       <c r="C64" t="n">
-        <v>0.423</v>
+        <v>0.425</v>
       </c>
       <c r="D64" t="s">
         <v>86</v>
       </c>
       <c r="E64" t="n">
-        <v>0.357</v>
+        <v>0.376</v>
       </c>
       <c r="F64" t="n">
-        <v>0.066</v>
+        <v>0.049</v>
       </c>
       <c r="G64" t="n">
-        <v>11079</v>
+        <v>11081</v>
       </c>
       <c r="H64" t="s">
         <v>81</v>
@@ -6710,16 +6710,16 @@
         <v>119</v>
       </c>
       <c r="C65" t="n">
-        <v>0.441</v>
+        <v>0.455</v>
       </c>
       <c r="D65" t="s">
         <v>86</v>
       </c>
       <c r="E65" t="n">
-        <v>0.338</v>
+        <v>0.331</v>
       </c>
       <c r="F65" t="n">
-        <v>0.103</v>
+        <v>0.124</v>
       </c>
       <c r="G65" t="n">
         <v>11074</v>
@@ -6796,16 +6796,16 @@
         <v>119</v>
       </c>
       <c r="C66" t="n">
-        <v>0.403</v>
+        <v>0.437</v>
       </c>
       <c r="D66" t="s">
         <v>86</v>
       </c>
       <c r="E66" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="F66" t="n">
-        <v>0.036</v>
+        <v>0.071</v>
       </c>
       <c r="G66" t="n">
         <v>11047</v>
@@ -6882,22 +6882,22 @@
         <v>86</v>
       </c>
       <c r="C67" t="n">
-        <v>0.473</v>
+        <v>0.482</v>
       </c>
       <c r="D67" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="E67" t="n">
-        <v>0.266</v>
+        <v>0.261</v>
       </c>
       <c r="F67" t="n">
-        <v>0.207</v>
+        <v>0.221</v>
       </c>
       <c r="G67" t="n">
-        <v>11073</v>
+        <v>11072</v>
       </c>
       <c r="H67" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="I67" t="s">
         <v>39</v>
@@ -7014,16 +7014,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.942100625</v>
+        <v>0.942136875</v>
       </c>
       <c r="F2" t="n">
         <v>0.957</v>
       </c>
       <c r="G2" t="n">
-        <v>0.88420125</v>
+        <v>0.88427375</v>
       </c>
       <c r="H2" t="n">
-        <v>0.96</v>
+        <v>0.95875</v>
       </c>
     </row>
     <row r="3">
@@ -7040,16 +7040,16 @@
         <v>0.72952380952381</v>
       </c>
       <c r="E3" t="n">
-        <v>0.617687619047619</v>
+        <v>0.617142857142857</v>
       </c>
       <c r="F3" t="n">
-        <v>0.605</v>
+        <v>0.603</v>
       </c>
       <c r="G3" t="n">
-        <v>0.386878095238095</v>
+        <v>0.384697142857143</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0285714285714286</v>
+        <v>0.0342857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -7063,19 +7063,19 @@
         <v>1075</v>
       </c>
       <c r="D4" t="n">
-        <v>0.96093023255814</v>
+        <v>0.965581395348837</v>
       </c>
       <c r="E4" t="n">
-        <v>0.67437023255814</v>
+        <v>0.672928372093023</v>
       </c>
       <c r="F4" t="n">
-        <v>0.702</v>
+        <v>0.696</v>
       </c>
       <c r="G4" t="n">
-        <v>0.486246511627907</v>
+        <v>0.483186046511628</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0818604651162791</v>
+        <v>0.0874418604651163</v>
       </c>
     </row>
   </sheetData>
@@ -7126,7 +7126,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.910779047619048</v>
+        <v>0.910550476190476</v>
       </c>
       <c r="F2" t="n">
         <v>0.902857142857143</v>
@@ -7146,10 +7146,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.957397209302326</v>
+        <v>0.957562790697674</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987906976744186</v>
+        <v>0.986046511627907</v>
       </c>
     </row>
     <row r="4">
@@ -7163,10 +7163,10 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="E4" t="n">
-        <v>0.45508</v>
+        <v>0.43328</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -7186,10 +7186,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.697423880597015</v>
+        <v>0.69844776119403</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0447761194029851</v>
+        <v>0.0537313432835821</v>
       </c>
     </row>
     <row r="6">
@@ -7206,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.51186</v>
+        <v>0.51344</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7223,10 +7223,10 @@
         <v>115</v>
       </c>
       <c r="D7" t="n">
-        <v>0.252173913043478</v>
+        <v>0.269565217391304</v>
       </c>
       <c r="E7" t="n">
-        <v>0.466773913043478</v>
+        <v>0.46535652173913</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7243,13 +7243,13 @@
         <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>0.985</v>
+        <v>0.99</v>
       </c>
       <c r="E8" t="n">
-        <v>0.70004</v>
+        <v>0.69679</v>
       </c>
       <c r="F8" t="n">
-        <v>0.035</v>
+        <v>0.0325</v>
       </c>
     </row>
     <row r="9">
@@ -7263,13 +7263,13 @@
         <v>450</v>
       </c>
       <c r="D9" t="n">
-        <v>0.933333333333333</v>
+        <v>0.942222222222222</v>
       </c>
       <c r="E9" t="n">
-        <v>0.718151111111111</v>
+        <v>0.719344444444444</v>
       </c>
       <c r="F9" t="n">
-        <v>0.164444444444444</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="10">
@@ -7283,10 +7283,10 @@
         <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>0.973333333333333</v>
+        <v>0.968888888888889</v>
       </c>
       <c r="E10" t="n">
-        <v>0.541173333333333</v>
+        <v>0.537675555555556</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
